--- a/data/trans_orig/P16A08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35903</t>
+          <t>35649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>62718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54623</t>
+          <t>53638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88142</t>
+          <t>85613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1001509</t>
+          <t>1000459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1019309</t>
+          <t>1019181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1251967</t>
+          <t>1252395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1279210</t>
+          <t>1279464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2258693</t>
+          <t>2261222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2292212</t>
+          <t>2293197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51692</t>
+          <t>51036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51709</t>
+          <t>51316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81470</t>
+          <t>82223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82738</t>
+          <t>80607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123743</t>
+          <t>120718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1640702</t>
+          <t>1641358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1667320</t>
+          <t>1667105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1506203</t>
+          <t>1505450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1535964</t>
+          <t>1536357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3156324</t>
+          <t>3159349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3197329</t>
+          <t>3199460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>34867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30347</t>
+          <t>30567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56222</t>
+          <t>56329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517750</t>
+          <t>516541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537155</t>
+          <t>537161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446065</t>
+          <t>445845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465417</t>
+          <t>464735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971598</t>
+          <t>971491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>997608</t>
+          <t>997934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61545</t>
+          <t>61076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98468</t>
+          <t>96429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110742</t>
+          <t>110391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>157218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180513</t>
+          <t>182254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242450</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3177057</t>
+          <t>3179096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3213980</t>
+          <t>3214449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3224248</t>
+          <t>3221979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3268455</t>
+          <t>3268806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6412272</t>
+          <t>6411768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6474209</t>
+          <t>6472468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45163</t>
+          <t>46307</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75255</t>
+          <t>78178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69203</t>
+          <t>69067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107236</t>
+          <t>107091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>932372</t>
+          <t>931508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>954996</t>
+          <t>954212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1257336</t>
+          <t>1254413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1287428</t>
+          <t>1286284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2197192</t>
+          <t>2197337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2235225</t>
+          <t>2235361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50243</t>
+          <t>50289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82411</t>
+          <t>85100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82636</t>
+          <t>83932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123773</t>
+          <t>123536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142001</t>
+          <t>145203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193965</t>
+          <t>196100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1877611</t>
+          <t>1874922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1909779</t>
+          <t>1909733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1626989</t>
+          <t>1627226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1668126</t>
+          <t>1666830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3516819</t>
+          <t>3514684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3568783</t>
+          <t>3565581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37756</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45060</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42830</t>
+          <t>43591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76275</t>
+          <t>75683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>442576</t>
+          <t>443197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464883</t>
+          <t>464638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>412594</t>
+          <t>411222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>435383</t>
+          <t>435003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>861711</t>
+          <t>862303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>895156</t>
+          <t>894395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>95331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140813</t>
+          <t>139389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167543</t>
+          <t>168086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224798</t>
+          <t>225297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276243</t>
+          <t>278900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>346025</t>
+          <t>348451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3271378</t>
+          <t>3272802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3317303</t>
+          <t>3316860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3316209</t>
+          <t>3315710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3373464</t>
+          <t>3372921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6607173</t>
+          <t>6604747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6676955</t>
+          <t>6674298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>30401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>28258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>55315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77815</t>
+          <t>75876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>723605</t>
+          <t>723946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>741677</t>
+          <t>741570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>939627</t>
+          <t>939345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>966779</t>
+          <t>966402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1671192</t>
+          <t>1673131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1702532</t>
+          <t>1702338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>75646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92191</t>
+          <t>92531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134930</t>
+          <t>133743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145173</t>
+          <t>143775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>199200</t>
+          <t>197061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2001040</t>
+          <t>2000739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2030285</t>
+          <t>2031020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1853370</t>
+          <t>1854557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1896109</t>
+          <t>1895769</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3865485</t>
+          <t>3867624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3919512</t>
+          <t>3920910</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>14836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36809</t>
+          <t>35815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27346</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>52597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81092</t>
+          <t>81759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510077</t>
+          <t>511071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530834</t>
+          <t>532050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497008</t>
+          <t>496543</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>521794</t>
+          <t>521710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1014935</t>
+          <t>1014268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1047247</t>
+          <t>1047260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85621</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126533</t>
+          <t>127696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159880</t>
+          <t>162585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214817</t>
+          <t>215981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261469</t>
+          <t>261876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>327985</t>
+          <t>330370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3251085</t>
+          <t>3249922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3291997</t>
+          <t>3290931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3317283</t>
+          <t>3316119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3372220</t>
+          <t>3369515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6581733</t>
+          <t>6579348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6648249</t>
+          <t>6647842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34846</t>
+          <t>34538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46578</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495960</t>
+          <t>495885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>509080</t>
+          <t>509017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>716886</t>
+          <t>717194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>731792</t>
+          <t>732605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218605</t>
+          <t>1219114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1238204</t>
+          <t>1238810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113852</t>
+          <t>109974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89688</t>
+          <t>89780</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>412217</t>
+          <t>425020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172836</t>
+          <t>170803</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>512200</t>
+          <t>534794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2176475</t>
+          <t>2180353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2230922</t>
+          <t>2234998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1824928</t>
+          <t>1812125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2147457</t>
+          <t>2147365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4015272</t>
+          <t>3992678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4354636</t>
+          <t>4356669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>30007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50327</t>
+          <t>50777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40805</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>70396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616574</t>
+          <t>616616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636873</t>
+          <t>637293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>610136</t>
+          <t>609686</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>632451</t>
+          <t>632417</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1236723</t>
+          <t>1236690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1266281</t>
+          <t>1265241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82984</t>
+          <t>83500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140785</t>
+          <t>141787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155608</t>
+          <t>153177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514848</t>
+          <t>492338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258065</t>
+          <t>260606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>617058</t>
+          <t>574267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3309617</t>
+          <t>3308615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3367418</t>
+          <t>3366902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3134491</t>
+          <t>3157001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3493731</t>
+          <t>3496162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6482684</t>
+          <t>6525475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6841677</t>
+          <t>6839136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>30660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62718</t>
+          <t>62995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>54551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85613</t>
+          <t>85705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1000459</t>
+          <t>1001063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1019181</t>
+          <t>1019135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1252395</t>
+          <t>1252118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1279464</t>
+          <t>1278745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2261222</t>
+          <t>2261130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2293197</t>
+          <t>2292284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51036</t>
+          <t>50859</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51316</t>
+          <t>50632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82223</t>
+          <t>82106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80607</t>
+          <t>82545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120718</t>
+          <t>122111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1641358</t>
+          <t>1641535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1667105</t>
+          <t>1666924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1505450</t>
+          <t>1505567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1536357</t>
+          <t>1537041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3159349</t>
+          <t>3157956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3199460</t>
+          <t>3197522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30567</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56329</t>
+          <t>55277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516541</t>
+          <t>518361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537161</t>
+          <t>537182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445845</t>
+          <t>445379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>464735</t>
+          <t>464720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971491</t>
+          <t>972543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>997934</t>
+          <t>998697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61076</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96429</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>112128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157218</t>
+          <t>156802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182254</t>
+          <t>181916</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242954</t>
+          <t>238183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3179096</t>
+          <t>3178164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3214449</t>
+          <t>3213719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3221979</t>
+          <t>3222395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3268806</t>
+          <t>3267069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6411768</t>
+          <t>6416539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6472468</t>
+          <t>6472806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>39721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46307</t>
+          <t>44042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78178</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69067</t>
+          <t>68956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107091</t>
+          <t>107922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>931508</t>
+          <t>932116</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>954212</t>
+          <t>954139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1254413</t>
+          <t>1257743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1286284</t>
+          <t>1288549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2197337</t>
+          <t>2196506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2235361</t>
+          <t>2235472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50289</t>
+          <t>51178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85100</t>
+          <t>84053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83932</t>
+          <t>83941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123536</t>
+          <t>124743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145203</t>
+          <t>142987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196100</t>
+          <t>195381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1874922</t>
+          <t>1875969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1909733</t>
+          <t>1908844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1627226</t>
+          <t>1626019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1666830</t>
+          <t>1666821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3514684</t>
+          <t>3515403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3565581</t>
+          <t>3567797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>39076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>46264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43591</t>
+          <t>44607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75683</t>
+          <t>77468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443197</t>
+          <t>441256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464638</t>
+          <t>464814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>411222</t>
+          <t>411390</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>435003</t>
+          <t>434722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>862303</t>
+          <t>860518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>894395</t>
+          <t>893379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95331</t>
+          <t>94776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139389</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168086</t>
+          <t>168124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225297</t>
+          <t>223023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278900</t>
+          <t>277482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348451</t>
+          <t>350660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3272802</t>
+          <t>3272393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3316860</t>
+          <t>3317415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3315710</t>
+          <t>3317984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3372921</t>
+          <t>3372883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6604747</t>
+          <t>6602538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6674298</t>
+          <t>6675716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30401</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28258</t>
+          <t>28390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55315</t>
+          <t>55884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46669</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75876</t>
+          <t>76662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>723946</t>
+          <t>723616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>741570</t>
+          <t>741437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>939345</t>
+          <t>938776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>966402</t>
+          <t>966270</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1673131</t>
+          <t>1672345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1702338</t>
+          <t>1703018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45365</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75646</t>
+          <t>78665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92531</t>
+          <t>91470</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133743</t>
+          <t>132586</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143775</t>
+          <t>147252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197061</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2000739</t>
+          <t>1997720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2031020</t>
+          <t>2031716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1854557</t>
+          <t>1855714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1895769</t>
+          <t>1896830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3867624</t>
+          <t>3867339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3920910</t>
+          <t>3917433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>37630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52597</t>
+          <t>53682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81759</t>
+          <t>82516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511071</t>
+          <t>509256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532050</t>
+          <t>530801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496543</t>
+          <t>495458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>521710</t>
+          <t>521163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1014268</t>
+          <t>1013511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1047260</t>
+          <t>1047059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86687</t>
+          <t>85477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127696</t>
+          <t>127005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162585</t>
+          <t>165838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215981</t>
+          <t>222815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261876</t>
+          <t>258822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330370</t>
+          <t>328197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3249922</t>
+          <t>3250613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3290931</t>
+          <t>3292141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3316119</t>
+          <t>3309285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3369515</t>
+          <t>3366262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6579348</t>
+          <t>6581521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6647842</t>
+          <t>6650896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>30664</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>39244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>51683</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>504693</t>
+          <t>567587</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495885</t>
+          <t>559358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>509017</t>
+          <t>572604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>725436</t>
+          <t>789121</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>717194</t>
+          <t>780541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>732605</t>
+          <t>797070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1230128</t>
+          <t>1356709</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1219114</t>
+          <t>1345149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1238810</t>
+          <t>1366294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85028</t>
+          <t>86865</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109974</t>
+          <t>112265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>166013</t>
+          <t>110533</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89780</t>
+          <t>89899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>425020</t>
+          <t>129359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>251041</t>
+          <t>197397</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170803</t>
+          <t>169477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>534794</t>
+          <t>225910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2205299</t>
+          <t>2143701</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2180353</t>
+          <t>2118301</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2234998</t>
+          <t>2162910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2071132</t>
+          <t>2060174</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1812125</t>
+          <t>2041348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2147365</t>
+          <t>2080808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4276431</t>
+          <t>4203877</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3992678</t>
+          <t>4175364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4356669</t>
+          <t>4231797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>32465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>43725</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>57908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54504</t>
+          <t>65065</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70396</t>
+          <t>86075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>629492</t>
+          <t>690247</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616616</t>
+          <t>679122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637293</t>
+          <t>699016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>623090</t>
+          <t>691152</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609686</t>
+          <t>676969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>632417</t>
+          <t>701416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1252582</t>
+          <t>1381399</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1236690</t>
+          <t>1360389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1265241</t>
+          <t>1395135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>110918</t>
+          <t>117664</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83500</t>
+          <t>96599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141787</t>
+          <t>145640</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153177</t>
+          <t>162735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>492338</t>
+          <t>210087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>340600</t>
+          <t>302586</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>260606</t>
+          <t>270447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>574267</t>
+          <t>337098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3339484</t>
+          <t>3401536</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3308615</t>
+          <t>3373560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3366902</t>
+          <t>3422601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3419657</t>
+          <t>3540448</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3157001</t>
+          <t>3515282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3496162</t>
+          <t>3562634</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6759142</t>
+          <t>6941984</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6525475</t>
+          <t>6907472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6839136</t>
+          <t>6974123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
